--- a/docs/后勤-矿物.xlsx
+++ b/docs/后勤-矿物.xlsx
@@ -1750,7 +1750,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
+    <row r="6" ht="150" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>燃料桶</t>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>硬度 3.0 / 抗爆 6.0；镐；可竖放/横放；单格 32000 mB，同轴最多两格共享 64000 mB，每格独立保存；竖直下方 master，水平先放者 master（同 tick 坐标较小）；油品及组件兼容才连接，第三格独立；斧切轴按 master 优先拆分；采集时剩余桶优先填满，余量随掉落保留；稳定 FluidHandler；比较器 0–15；不可活塞推动，不可作燃料</t>
+          <t>硬度 3.0 / 抗爆 6.0；镐；可竖放/横放；fuelBarrelCapacity 配置单格容量，默认 16000 mB；fuelBarrelAxialConnection 默认开启，仅在放置时记录，关闭后新桶独立，已有桶策略不变；默认单格 16000 mB（16 桶），同轴两格共享 32000 mB（32 桶），每格独立保存；竖直下方 master，水平先放者 master（同 tick 坐标较小）；油品及组件兼容才连接，第三格独立；斧切轴按 master 优先拆分；采集时剩余桶优先填满，余量随掉落保留；稳定 FluidHandler；比较器 0–15；不可活塞推动，不可作燃料；降容保留旧存量，超额可抽取，禁止继续灌入</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">

--- a/docs/后勤-矿物.xlsx
+++ b/docs/后勤-矿物.xlsx
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>硬度 0.5 / 抗爆 0.5；空手可采、锹加速；固定掉落 2–4 硝土，不受时运影响，任何情况下不超过 4；精准采集掉落自身</t>
+          <t>硬度0.5／抗爆0.5；空手可采，锹加速。非锹掉2–4硝土，锹固定4个，无时运加成；精准采集优先掉自身。</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
